--- a/docs/セットアップガイド.xlsx
+++ b/docs/セットアップガイド.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="203">
   <si>
     <t>環境セットアップガイド</t>
   </si>
@@ -134,6 +134,9 @@
   </si>
   <si>
     <t>確認・注意点</t>
+  </si>
+  <si>
+    <t>画像</t>
   </si>
   <si>
     <t>ダウンロードページを開く</t>
@@ -762,7 +765,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -783,6 +786,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -798,6 +802,455 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2190750" cy="1066800"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2190750" cy="1485900"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2190750" cy="1066800"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2190750" cy="1066800"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2190750" cy="1485900"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2190750" cy="1266825"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2190750" cy="1066800"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2190750" cy="1066800"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2190750" cy="1066800"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2190750" cy="1066800"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2190750" cy="1743075"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1343,7 +1796,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1353,10 +1806,10 @@
         <v>34</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" ht="56" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1364,10 +1817,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" ht="56" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1375,10 +1828,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" ht="56" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1386,10 +1839,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8" ht="56" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1397,10 +1850,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9" ht="56" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1408,10 +1861,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10" ht="56" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1419,10 +1872,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -1437,32 +1890,34 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="55" customWidth="1"/>
-    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="4" max="5" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-    </row>
-    <row r="4" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" s="2"/>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>34</v>
       </c>
@@ -1475,157 +1930,171 @@
       <c r="D4" s="6" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="5" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" ht="130" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>1</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+      <c r="E5" s="8"/>
+    </row>
+    <row r="6" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="E6" s="8"/>
+    </row>
+    <row r="7" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>3</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+      <c r="E7" s="8"/>
+    </row>
+    <row r="8" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>4</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="E8" s="8"/>
+    </row>
+    <row r="9" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>5</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="E9" s="8"/>
+    </row>
+    <row r="10" ht="130" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <v>6</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="E10" s="8"/>
+    </row>
+    <row r="11" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <v>7</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="E11" s="8"/>
+    </row>
+    <row r="12" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
         <v>8</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>61</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="E12" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="55" customWidth="1"/>
-    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="4" max="5" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-    </row>
-    <row r="4" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" s="2"/>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>34</v>
       </c>
@@ -1638,129 +2107,141 @@
       <c r="D4" s="6" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="5" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" ht="130" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>1</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+      <c r="E5" s="8"/>
+    </row>
+    <row r="6" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+      <c r="E6" s="8"/>
+    </row>
+    <row r="7" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>3</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="E7" s="8"/>
+    </row>
+    <row r="8" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>4</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+      <c r="E8" s="8"/>
+    </row>
+    <row r="9" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>5</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="10" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+      <c r="E9" s="8"/>
+    </row>
+    <row r="10" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <v>6</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>75</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="E10" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="55" customWidth="1"/>
-    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="4" max="5" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-    </row>
-    <row r="4" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" s="2"/>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>34</v>
       </c>
@@ -1773,210 +2254,228 @@
       <c r="D4" s="6" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="5" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" ht="130" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>1</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="E5" s="8"/>
+    </row>
+    <row r="6" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="7" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+      <c r="E6" s="8"/>
+    </row>
+    <row r="7" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>3</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="8" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+      <c r="E7" s="8"/>
+    </row>
+    <row r="8" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>4</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="9" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+      <c r="E8" s="8"/>
+    </row>
+    <row r="9" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>5</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+      <c r="E9" s="8"/>
+    </row>
+    <row r="10" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <v>6</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="11" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+      <c r="E10" s="8"/>
+    </row>
+    <row r="11" ht="130" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <v>7</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="12" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+      <c r="E11" s="8"/>
+    </row>
+    <row r="12" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
         <v>8</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="13" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+      <c r="E12" s="8"/>
+    </row>
+    <row r="13" ht="130" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
         <v>9</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="14" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="E13" s="8"/>
+    </row>
+    <row r="14" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>10</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="15" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E14" s="8"/>
+    </row>
+    <row r="15" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
         <v>11</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+      <c r="E15" s="8"/>
+    </row>
+    <row r="16" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
         <v>12</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="17" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="E16" s="8"/>
+    </row>
+    <row r="17" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="7">
         <v>13</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="18" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+      <c r="E17" s="8"/>
+    </row>
+    <row r="18" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
         <v>14</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>111</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="E18" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2001,7 +2500,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2026,13 +2525,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2040,13 +2539,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2054,13 +2553,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2068,13 +2567,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2082,13 +2581,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -2122,7 +2621,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2147,13 +2646,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2161,13 +2660,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2175,13 +2674,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2189,13 +2688,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2203,13 +2702,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2217,13 +2716,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -2257,7 +2756,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2282,13 +2781,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2296,13 +2795,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2310,13 +2809,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -2331,32 +2830,34 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="55" customWidth="1"/>
-    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="4" max="5" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-    </row>
-    <row r="4" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" s="2"/>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>34</v>
       </c>
@@ -2369,98 +2870,108 @@
       <c r="D4" s="6" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="5" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" ht="130" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>1</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="6" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+      <c r="E5" s="8"/>
+    </row>
+    <row r="6" ht="130" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="7" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+      <c r="E6" s="8"/>
+    </row>
+    <row r="7" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>3</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="8" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="E7" s="8"/>
+    </row>
+    <row r="8" ht="130" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>4</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="9" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+      <c r="E8" s="8"/>
+    </row>
+    <row r="9" ht="130" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>5</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="10" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+      <c r="E9" s="8"/>
+    </row>
+    <row r="10" ht="130" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <v>6</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>171</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="E10" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2485,7 +2996,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2510,13 +3021,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2524,13 +3035,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2538,13 +3049,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2552,13 +3063,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2566,13 +3077,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
